--- a/artfynd/A 40684-2025 artfynd.xlsx
+++ b/artfynd/A 40684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128109244</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128109272</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128109309</v>
       </c>
       <c r="B4" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40684-2025 artfynd.xlsx
+++ b/artfynd/A 40684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128109244</v>
       </c>
       <c r="B2" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128109272</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128109309</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40684-2025 artfynd.xlsx
+++ b/artfynd/A 40684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128109244</v>
       </c>
       <c r="B2" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128109272</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128109309</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
